--- a/evaluacion/hoja_rapida_evaluacion.xlsx
+++ b/evaluacion/hoja_rapida_evaluacion.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Registro" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Comentarios" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Leyenda" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registro" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comentarios" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leyenda" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -608,100 +608,388 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
-      <c r="P2" s="2" t="n"/>
-      <c r="Q2" s="2" t="n"/>
-      <c r="R2" s="2" t="n"/>
-      <c r="S2" s="2" t="n"/>
-      <c r="T2" s="2" t="n"/>
-      <c r="U2" s="2" t="n"/>
-      <c r="V2" s="2" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Héctor</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>OLIBOT</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Letras básicas (nivel rojo); trazos de pintura</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Técnico</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Sí (botón repetir, autónomo)</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>Contento</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>Mal</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Niño prueba / dificultades. No espera tutorial. Completa 4 ejercicios de pintura. Prefiere OLIBOT al papel ('más divertido'). No le gusta que repitan 'Muy bien otra vez'. Reducir preguntas de estado emocional. Quiere dibujo libre.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="3" t="n"/>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n"/>
-      <c r="M3" s="3" t="n"/>
-      <c r="N3" s="3" t="n"/>
-      <c r="O3" s="3" t="n"/>
-      <c r="P3" s="3" t="n"/>
-      <c r="Q3" s="3" t="n"/>
-      <c r="R3" s="3" t="n"/>
-      <c r="S3" s="3" t="n"/>
-      <c r="T3" s="3" t="n"/>
-      <c r="U3" s="3" t="n"/>
-      <c r="V3" s="3" t="n"/>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Cayetana</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>OLIBOT</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>a, as, l</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>Pedagógico</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>Contento</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>No usó</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>Nivel automático → rojo. Trabaja a, as, l. Sin miedo; ríe. Paciente, espera los estados. Se cansa al final y pinta. Selecciona dibujo por preferencia, no por categoría.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n"/>
-      <c r="L4" s="2" t="n"/>
-      <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2" t="n"/>
-      <c r="P4" s="2" t="n"/>
-      <c r="Q4" s="2" t="n"/>
-      <c r="R4" s="2" t="n"/>
-      <c r="S4" s="2" t="n"/>
-      <c r="T4" s="2" t="n"/>
-      <c r="U4" s="2" t="n"/>
-      <c r="V4" s="2" t="n"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Ángela</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>OLIBOT</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>A (nivel rojo; ella dice ya sabérsela). Le gustaría matemáticas.</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Técnico</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>Contento</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>No usó</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>4 años, nivel rojo. Atiende bien el tutorial la 1ª vez; después lo ignora (pq se lo sabe). Va a pintar a los 5 min. Aprende botones con 1 demo. A veces selección accidental con el lápiz. Le gustaría tener matemáticas.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="3" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="n"/>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="n"/>
-      <c r="P5" s="3" t="n"/>
-      <c r="Q5" s="3" t="n"/>
-      <c r="R5" s="3" t="n"/>
-      <c r="S5" s="3" t="n"/>
-      <c r="T5" s="3" t="n"/>
-      <c r="U5" s="3" t="n"/>
-      <c r="V5" s="3" t="n"/>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Oliver</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>OLIBOT</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Línea recta, línea curva, l, 2, 3</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Técnico</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>Sí (vuelve espontáneamente a 2 y 3)</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>Contento</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>No usó</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>3 años — el que más aguanta (29 min). Le flipan las animaciones y los círculos verdes. Entiende la goma y el sistema de estrellas. Vuelve a números 2 y 3 por iniciativa propia. 2 min de pintura al final.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="n"/>
@@ -2049,34 +2337,34 @@
     </row>
   </sheetData>
   <dataValidations count="10">
-    <dataValidation sqref="D2:D301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Individual,Pareja"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"OLIBOT,Papel"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"3,4,5,6"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Amarillo,Verde,Azul,Rojo"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Técnico,Pedagógico,Emocional,Ninguno"</formula1>
     </dataValidation>
-    <dataValidation sqref="R2:R301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="R2:R301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Contento,Normal,Triste"</formula1>
     </dataValidation>
-    <dataValidation sqref="S2:S301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="S2:S301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="T2:T301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="T2:T301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Alta,Media,Baja"</formula1>
     </dataValidation>
-    <dataValidation sqref="U2:U301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U2:U301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Bien,Regular,Mal,No usó"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2122,100 +2410,356 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Héctor</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Se le dio bien</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Completó 4 ejercicios en el módulo de pintura sin que se lo pidieran. Recuerda y usa el botón de repetir de forma autónoma. Comparación espontánea con papel: 'le gusta más OLIBOT, más divertido'.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="3" t="n"/>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Héctor</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Le costó / se atascó</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>No espera el fin del tutorial; lo salta porque 'ya se lo sabe'. Muy lento al procesar niveles avanzados (azul/rojo). No espera el final de las animaciones. No sabe dónde está la goma en el módulo de dibujo.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Héctor</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Voz / habla</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Quitó el micrófono; no usó la voz para hablar con OLIBOT. Sin embargo le gustó MUCHO escuchar a OLIBOT hablar (TTS).</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="3" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Héctor</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Actitud / emoción</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Activo e impaciente con el tutorial; disfruta activamente la pintura. Le gusta más OLIBOT que las fichas de papel ('más divertido').</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Héctor</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Idea de mejora</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1) No repetir tanto '¡Muy bien! Otra vez'. 2) Reducir la frecuencia de preguntas sobre el estado emocional. 3) Añadir opción de dibujo libre. 4) Revisar la claridad del espacio del tutorial.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="3" t="n"/>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Héctor</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Incidencia técnica</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Quitó el micrófono durante la sesión. El espacio del tutorial no se entendió a primer vistazo.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Cayetana</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Se le dio bien</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Pasó todos los niveles de tirón con nivel automático (sin resistencia). Espera las transiciones y estados de OLIBOT con paciencia. Contesta las preguntas de OLIBOT y ríe (sin miedo).</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="3" t="n"/>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Cayetana</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Le costó / se atascó</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Se cansó en la letra 'l' → necesitó cambio de actividad (primero a números, luego volvió a 'l'). Selecciona el dibujo que le gusta por preferencia personal, no por categoría curricular.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="2" t="n"/>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Cayetana</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Actitud / emoción</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Sin miedo. Tranquila y paciente durante toda la sesión. No se queja aunque ya conoce el contenido → actitud muy positiva.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="3" t="n"/>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Ángela</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Se le dio bien</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Atendió muy bien el tutorial la primera vez. Aprendió todos los botones con una sola demostración del adulto. Maneja la tablet con soltura (4 años).</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="2" t="n"/>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Ángela</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Le costó / se atascó</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Mantener el foco en la escritura: a los 5 min (10:40) pasó a pintar voluntariamente. Selección accidental de elementos con el lápiz/pincel táctil. Después de la 1ª vez ya no atiende al tutorial (pq se lo sabe).</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="3" t="n"/>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Ángela</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Actitud / emoción</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Confiada y exploradora. Le gustaría que OLIBOT tuviera matemáticas (feedback espontáneo de contenido, muy relevante).</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="2" t="n"/>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Ángela</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Idea de mejora</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Los niños pequeños van directos a pintar cuando tienen la opción → gestionar la transición escritura→pintura. Revisar el comportamiento del lápiz táctil en tablet (selección accidental). Considerar añadir contenido de matemáticas.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="3" t="n"/>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Oliver</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Se le dio bien</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Trazos básicos: línea recta, línea curva, 'l'. Entiende perfectamente la goma. Comprende el sistema de estrellas para ganar. Vuelve espontáneamente a los números 2 y 3 para seguir practicando.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="2" t="n"/>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Oliver</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Actitud / emoción</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Muy motivado y entusiasta. Las animaciones y los círculos verdes le 'flipan'. Le gusta el avatar, el confeti y 'ganar el 10'. Es el niño que MÁS aguanta de la sesión (29 min) a pesar de ser el más pequeño (3 años).</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Oliver</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Anécdota / frase</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>'Es el que aguanta.' Contrasta claramente con los niños mayores que se cansaron antes. A las 12:00 pasó voluntariamente a pintar pero solo duró 2 min. Dice verbalmente que le gusta (feedback espontáneo).</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="2" t="n"/>
@@ -2603,7 +3147,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="C2:C401" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C401" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Se le dio bien,Le costó / se atascó,Voz / habla,Anécdota / frase,Actitud / emoción,Incidencia técnica,Dinámica de pareja,Idea de mejora"</formula1>
     </dataValidation>
   </dataValidations>
